--- a/synthetic/output/incentive_rules/incentive_rules.xlsx
+++ b/synthetic/output/incentive_rules/incentive_rules.xlsx
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -510,7 +510,7 @@
         <v>50000</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -565,10 +565,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -623,10 +623,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>5</v>
@@ -681,10 +681,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -713,7 +713,7 @@
         <v>100000</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -858,7 +858,7 @@
         <v>100000</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -884,10 +884,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G16" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G19" t="n">
         <v>4</v>
@@ -1003,7 +1003,7 @@
         <v>100000</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -1061,7 +1061,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G23" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G24" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="G25" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -1264,7 +1264,7 @@
         <v>100000</v>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -1322,7 +1322,7 @@
         <v>50000</v>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
